--- a/artfynd/A 55957-2025 artfynd.xlsx
+++ b/artfynd/A 55957-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>130252661</v>
       </c>
       <c r="B2" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130252658</v>
       </c>
       <c r="B3" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130252662</v>
+        <v>130252213</v>
       </c>
       <c r="B4" t="n">
-        <v>92923</v>
+        <v>93010</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496302</v>
+        <v>496229</v>
       </c>
       <c r="R4" t="n">
-        <v>6828945</v>
+        <v>6828807</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -978,29 +978,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130252660</v>
+        <v>130252204</v>
       </c>
       <c r="B5" t="n">
-        <v>78852</v>
+        <v>79799</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1008,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1032,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496248</v>
+        <v>496196</v>
       </c>
       <c r="R5" t="n">
-        <v>6828803</v>
+        <v>6829176</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1077,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,44 +1091,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130252659</v>
+        <v>130252214</v>
       </c>
       <c r="B6" t="n">
-        <v>78852</v>
+        <v>93010</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496262</v>
+        <v>496220</v>
       </c>
       <c r="R6" t="n">
-        <v>6828867</v>
+        <v>6829188</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1184,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1199,15 +1198,2255 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130252205</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hammarberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>496203</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6829246</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130252208</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hammarberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>496072</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6828986</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130252207</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hammarberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>496116</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6829108</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130252662</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93010</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hammarberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>496302</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6828945</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Kajsa Larsson</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Kajsa Larsson</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130252211</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78937</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hammarberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>496196</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6829176</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130252206</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hammarberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>496198</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6829176</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130252212</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hammarberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>496212</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6829184</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130252209</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78937</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hammarberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>496215</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6829262</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130252660</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78937</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hammarberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>496248</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6828803</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130252210</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78937</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hammarberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>496222</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6829194</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130252659</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78937</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hammarberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>496262</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6828867</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130256006</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hammarberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>496064</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6829002</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130256321</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78938</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hammarberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>496183</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6828767</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130256005</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hammarberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>496177</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6829128</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130256002</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78937</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hammarberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>496059</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6829006</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130256003</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hammarberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>496231</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6829125</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130256007</v>
+      </c>
+      <c r="B23" t="n">
+        <v>93010</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hammarberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>496230</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6828797</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130256000</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91712</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4660</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Rävticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Inocutis rheades</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hammarberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>496087</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6828938</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130256001</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78937</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hammarberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>496196</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6829166</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130256320</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78938</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hammarberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>496252</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6828819</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130256004</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hammarberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>496212</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6829243</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55957-2025 artfynd.xlsx
+++ b/artfynd/A 55957-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130252661</v>
       </c>
       <c r="B2" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130252658</v>
+        <v>130252213</v>
       </c>
       <c r="B3" t="n">
-        <v>78937</v>
+        <v>93013</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496322</v>
+        <v>496229</v>
       </c>
       <c r="R3" t="n">
-        <v>6828932</v>
+        <v>6828807</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,44 +877,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130252213</v>
+        <v>130252658</v>
       </c>
       <c r="B4" t="n">
-        <v>93010</v>
+        <v>78940</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496229</v>
+        <v>496322</v>
       </c>
       <c r="R4" t="n">
-        <v>6828807</v>
+        <v>6828932</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,12 +984,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -999,7 +999,7 @@
         <v>130252204</v>
       </c>
       <c r="B5" t="n">
-        <v>79799</v>
+        <v>79802</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>130252214</v>
       </c>
       <c r="B6" t="n">
-        <v>93010</v>
+        <v>93013</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>130252662</v>
       </c>
       <c r="B10" t="n">
-        <v>93010</v>
+        <v>93013</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>130252211</v>
       </c>
       <c r="B11" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>130252212</v>
       </c>
       <c r="B13" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>130252209</v>
       </c>
       <c r="B14" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>130252660</v>
       </c>
       <c r="B15" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>130252210</v>
       </c>
       <c r="B16" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>130252659</v>
       </c>
       <c r="B17" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>130256006</v>
       </c>
       <c r="B18" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>130256321</v>
       </c>
       <c r="B19" t="n">
-        <v>78938</v>
+        <v>78941</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>130256005</v>
       </c>
       <c r="B20" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>130256002</v>
       </c>
       <c r="B21" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>130256003</v>
       </c>
       <c r="B22" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>130256007</v>
       </c>
       <c r="B23" t="n">
-        <v>93010</v>
+        <v>93013</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>130256000</v>
       </c>
       <c r="B24" t="n">
-        <v>91712</v>
+        <v>91715</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>130256001</v>
       </c>
       <c r="B25" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>130256004</v>
       </c>
       <c r="B26" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>130256320</v>
       </c>
       <c r="B27" t="n">
-        <v>78938</v>
+        <v>78941</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 55957-2025 artfynd.xlsx
+++ b/artfynd/A 55957-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130252661</v>
       </c>
       <c r="B2" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130252213</v>
       </c>
       <c r="B3" t="n">
-        <v>93013</v>
+        <v>93039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130252658</v>
       </c>
       <c r="B4" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130252204</v>
       </c>
       <c r="B5" t="n">
-        <v>79802</v>
+        <v>79828</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>130252214</v>
       </c>
       <c r="B6" t="n">
-        <v>93013</v>
+        <v>93039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>130252662</v>
       </c>
       <c r="B10" t="n">
-        <v>93013</v>
+        <v>93039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>130252211</v>
       </c>
       <c r="B11" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>130252212</v>
       </c>
       <c r="B13" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>130252209</v>
       </c>
       <c r="B14" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>130252660</v>
       </c>
       <c r="B15" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>130252210</v>
       </c>
       <c r="B16" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>130252659</v>
       </c>
       <c r="B17" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>130256006</v>
       </c>
       <c r="B18" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>130256321</v>
       </c>
       <c r="B19" t="n">
-        <v>78941</v>
+        <v>78967</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>130256005</v>
       </c>
       <c r="B20" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>130256002</v>
       </c>
       <c r="B21" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2806,45 +2806,56 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130256003</v>
+        <v>130256007</v>
       </c>
       <c r="B22" t="n">
-        <v>79183</v>
+        <v>93039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hammarberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496231</v>
+        <v>496230</v>
       </c>
       <c r="R22" t="n">
-        <v>6829125</v>
+        <v>6828797</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2876,7 +2887,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2886,7 +2897,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2895,6 +2906,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2913,56 +2925,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130256007</v>
+        <v>130256003</v>
       </c>
       <c r="B23" t="n">
-        <v>93013</v>
+        <v>79209</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hammarberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496230</v>
+        <v>496231</v>
       </c>
       <c r="R23" t="n">
-        <v>6828797</v>
+        <v>6829125</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2994,7 +2995,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3004,7 +3005,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3013,7 +3014,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3035,7 +3035,7 @@
         <v>130256000</v>
       </c>
       <c r="B24" t="n">
-        <v>91715</v>
+        <v>91741</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>130256001</v>
       </c>
       <c r="B25" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3246,10 +3246,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130256004</v>
+        <v>130256320</v>
       </c>
       <c r="B26" t="n">
-        <v>79183</v>
+        <v>78967</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3257,21 +3257,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496212</v>
+        <v>496252</v>
       </c>
       <c r="R26" t="n">
-        <v>6829243</v>
+        <v>6828819</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3314,19 +3314,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3341,22 +3331,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130256320</v>
+        <v>130256004</v>
       </c>
       <c r="B27" t="n">
-        <v>78941</v>
+        <v>79209</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3364,21 +3354,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3388,10 +3378,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496252</v>
+        <v>496212</v>
       </c>
       <c r="R27" t="n">
-        <v>6828819</v>
+        <v>6829243</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3421,9 +3411,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3438,12 +3438,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 55957-2025 artfynd.xlsx
+++ b/artfynd/A 55957-2025 artfynd.xlsx
@@ -2806,56 +2806,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130256007</v>
+        <v>130256003</v>
       </c>
       <c r="B22" t="n">
-        <v>93039</v>
+        <v>79209</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hammarberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496230</v>
+        <v>496231</v>
       </c>
       <c r="R22" t="n">
-        <v>6828797</v>
+        <v>6829125</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2887,7 +2876,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2897,7 +2886,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2906,7 +2895,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2925,45 +2913,56 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130256003</v>
+        <v>130256007</v>
       </c>
       <c r="B23" t="n">
-        <v>79209</v>
+        <v>93039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hammarberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496231</v>
+        <v>496230</v>
       </c>
       <c r="R23" t="n">
-        <v>6829125</v>
+        <v>6828797</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2995,7 +2994,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3005,7 +3004,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,6 +3013,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55957-2025 artfynd.xlsx
+++ b/artfynd/A 55957-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>130252213</v>
       </c>
       <c r="B3" t="n">
-        <v>93039</v>
+        <v>93040</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>130252214</v>
       </c>
       <c r="B6" t="n">
-        <v>93039</v>
+        <v>93040</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>130252662</v>
       </c>
       <c r="B10" t="n">
-        <v>93039</v>
+        <v>93040</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2806,45 +2806,56 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130256003</v>
+        <v>130256007</v>
       </c>
       <c r="B22" t="n">
-        <v>79209</v>
+        <v>93040</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hammarberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496231</v>
+        <v>496230</v>
       </c>
       <c r="R22" t="n">
-        <v>6829125</v>
+        <v>6828797</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2876,7 +2887,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2886,7 +2897,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2895,6 +2906,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2913,56 +2925,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130256007</v>
+        <v>130256003</v>
       </c>
       <c r="B23" t="n">
-        <v>93039</v>
+        <v>79209</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hammarberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496230</v>
+        <v>496231</v>
       </c>
       <c r="R23" t="n">
-        <v>6828797</v>
+        <v>6829125</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2994,7 +2995,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3004,7 +3005,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3013,7 +3014,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3035,7 +3035,7 @@
         <v>130256000</v>
       </c>
       <c r="B24" t="n">
-        <v>91741</v>
+        <v>91742</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 55957-2025 artfynd.xlsx
+++ b/artfynd/A 55957-2025 artfynd.xlsx
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130252213</v>
+        <v>130252658</v>
       </c>
       <c r="B3" t="n">
-        <v>93040</v>
+        <v>78966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496229</v>
+        <v>496322</v>
       </c>
       <c r="R3" t="n">
-        <v>6828807</v>
+        <v>6828932</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,44 +877,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130252658</v>
+        <v>130252213</v>
       </c>
       <c r="B4" t="n">
-        <v>78966</v>
+        <v>93041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496322</v>
+        <v>496229</v>
       </c>
       <c r="R4" t="n">
-        <v>6828932</v>
+        <v>6828807</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,12 +984,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1106,7 +1106,7 @@
         <v>130252214</v>
       </c>
       <c r="B6" t="n">
-        <v>93040</v>
+        <v>93041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>130252662</v>
       </c>
       <c r="B10" t="n">
-        <v>93040</v>
+        <v>93041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>130256007</v>
       </c>
       <c r="B22" t="n">
-        <v>93040</v>
+        <v>93041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>130256000</v>
       </c>
       <c r="B24" t="n">
-        <v>91742</v>
+        <v>91743</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3246,10 +3246,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130256320</v>
+        <v>130256004</v>
       </c>
       <c r="B26" t="n">
-        <v>78967</v>
+        <v>79209</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3257,21 +3257,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496252</v>
+        <v>496212</v>
       </c>
       <c r="R26" t="n">
-        <v>6828819</v>
+        <v>6829243</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3314,9 +3314,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3331,22 +3341,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130256004</v>
+        <v>130256320</v>
       </c>
       <c r="B27" t="n">
-        <v>79209</v>
+        <v>78967</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3354,21 +3364,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3378,10 +3388,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496212</v>
+        <v>496252</v>
       </c>
       <c r="R27" t="n">
-        <v>6829243</v>
+        <v>6828819</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3411,19 +3421,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3438,12 +3438,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 55957-2025 artfynd.xlsx
+++ b/artfynd/A 55957-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130252661</v>
       </c>
       <c r="B2" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130252658</v>
+        <v>130252213</v>
       </c>
       <c r="B3" t="n">
-        <v>78966</v>
+        <v>93043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496322</v>
+        <v>496229</v>
       </c>
       <c r="R3" t="n">
-        <v>6828932</v>
+        <v>6828807</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,44 +877,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130252213</v>
+        <v>130252658</v>
       </c>
       <c r="B4" t="n">
-        <v>93041</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496229</v>
+        <v>496322</v>
       </c>
       <c r="R4" t="n">
-        <v>6828807</v>
+        <v>6828932</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,12 +984,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -999,7 +999,7 @@
         <v>130252204</v>
       </c>
       <c r="B5" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>130252214</v>
       </c>
       <c r="B6" t="n">
-        <v>93041</v>
+        <v>93043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>130252662</v>
       </c>
       <c r="B10" t="n">
-        <v>93041</v>
+        <v>93043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>130252211</v>
       </c>
       <c r="B11" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>130252212</v>
       </c>
       <c r="B13" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>130252209</v>
       </c>
       <c r="B14" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>130252660</v>
       </c>
       <c r="B15" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>130252210</v>
       </c>
       <c r="B16" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>130252659</v>
       </c>
       <c r="B17" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>130256006</v>
       </c>
       <c r="B18" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>130256321</v>
       </c>
       <c r="B19" t="n">
-        <v>78967</v>
+        <v>78969</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>130256005</v>
       </c>
       <c r="B20" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>130256002</v>
       </c>
       <c r="B21" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>130256007</v>
       </c>
       <c r="B22" t="n">
-        <v>93041</v>
+        <v>93043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>130256003</v>
       </c>
       <c r="B23" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>130256000</v>
       </c>
       <c r="B24" t="n">
-        <v>91743</v>
+        <v>91745</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>130256001</v>
       </c>
       <c r="B25" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3246,10 +3246,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130256004</v>
+        <v>130256320</v>
       </c>
       <c r="B26" t="n">
-        <v>79209</v>
+        <v>78969</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3257,21 +3257,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496212</v>
+        <v>496252</v>
       </c>
       <c r="R26" t="n">
-        <v>6829243</v>
+        <v>6828819</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3314,19 +3314,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3341,22 +3331,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130256320</v>
+        <v>130256004</v>
       </c>
       <c r="B27" t="n">
-        <v>78967</v>
+        <v>79211</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3364,21 +3354,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3388,10 +3378,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496252</v>
+        <v>496212</v>
       </c>
       <c r="R27" t="n">
-        <v>6828819</v>
+        <v>6829243</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3421,9 +3411,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3438,12 +3438,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 55957-2025 artfynd.xlsx
+++ b/artfynd/A 55957-2025 artfynd.xlsx
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130252213</v>
+        <v>130252658</v>
       </c>
       <c r="B3" t="n">
-        <v>93043</v>
+        <v>78968</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496229</v>
+        <v>496322</v>
       </c>
       <c r="R3" t="n">
-        <v>6828807</v>
+        <v>6828932</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,44 +877,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130252658</v>
+        <v>130252213</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>93047</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496322</v>
+        <v>496229</v>
       </c>
       <c r="R4" t="n">
-        <v>6828932</v>
+        <v>6828807</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,12 +984,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1106,7 +1106,7 @@
         <v>130252214</v>
       </c>
       <c r="B6" t="n">
-        <v>93043</v>
+        <v>93047</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>130252662</v>
       </c>
       <c r="B10" t="n">
-        <v>93043</v>
+        <v>93047</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2806,56 +2806,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130256007</v>
+        <v>130256003</v>
       </c>
       <c r="B22" t="n">
-        <v>93043</v>
+        <v>79211</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hammarberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496230</v>
+        <v>496231</v>
       </c>
       <c r="R22" t="n">
-        <v>6828797</v>
+        <v>6829125</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2887,7 +2876,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2897,7 +2886,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2906,7 +2895,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2925,45 +2913,56 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130256003</v>
+        <v>130256007</v>
       </c>
       <c r="B23" t="n">
-        <v>79211</v>
+        <v>93047</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hammarberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496231</v>
+        <v>496230</v>
       </c>
       <c r="R23" t="n">
-        <v>6829125</v>
+        <v>6828797</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2995,7 +2994,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3005,7 +3004,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,6 +3013,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55957-2025 artfynd.xlsx
+++ b/artfynd/A 55957-2025 artfynd.xlsx
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130252658</v>
+        <v>130252213</v>
       </c>
       <c r="B3" t="n">
-        <v>78968</v>
+        <v>93047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496322</v>
+        <v>496229</v>
       </c>
       <c r="R3" t="n">
-        <v>6828932</v>
+        <v>6828807</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,44 +877,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130252213</v>
+        <v>130252658</v>
       </c>
       <c r="B4" t="n">
-        <v>93047</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496229</v>
+        <v>496322</v>
       </c>
       <c r="R4" t="n">
-        <v>6828807</v>
+        <v>6828932</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,12 +984,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -2388,10 +2388,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130256006</v>
+        <v>130256321</v>
       </c>
       <c r="B18" t="n">
-        <v>79211</v>
+        <v>78969</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2399,21 +2399,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2423,10 +2423,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496064</v>
+        <v>496183</v>
       </c>
       <c r="R18" t="n">
-        <v>6829002</v>
+        <v>6828767</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2456,19 +2456,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2483,22 +2473,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130256321</v>
+        <v>130256006</v>
       </c>
       <c r="B19" t="n">
-        <v>78969</v>
+        <v>79211</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2506,21 +2496,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2530,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496183</v>
+        <v>496064</v>
       </c>
       <c r="R19" t="n">
-        <v>6828767</v>
+        <v>6829002</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2563,9 +2553,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2580,12 +2580,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130256320</v>
+        <v>130256004</v>
       </c>
       <c r="B26" t="n">
-        <v>78969</v>
+        <v>79211</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3257,21 +3257,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496252</v>
+        <v>496212</v>
       </c>
       <c r="R26" t="n">
-        <v>6828819</v>
+        <v>6829243</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3314,9 +3314,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3331,22 +3341,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130256004</v>
+        <v>130256320</v>
       </c>
       <c r="B27" t="n">
-        <v>79211</v>
+        <v>78969</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3354,21 +3364,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3378,10 +3388,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496212</v>
+        <v>496252</v>
       </c>
       <c r="R27" t="n">
-        <v>6829243</v>
+        <v>6828819</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3411,19 +3421,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3438,12 +3438,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 55957-2025 artfynd.xlsx
+++ b/artfynd/A 55957-2025 artfynd.xlsx
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130252213</v>
+        <v>130252658</v>
       </c>
       <c r="B3" t="n">
-        <v>93047</v>
+        <v>78968</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496229</v>
+        <v>496322</v>
       </c>
       <c r="R3" t="n">
-        <v>6828807</v>
+        <v>6828932</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,44 +877,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130252658</v>
+        <v>130252213</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>93047</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496322</v>
+        <v>496229</v>
       </c>
       <c r="R4" t="n">
-        <v>6828932</v>
+        <v>6828807</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,12 +984,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -2388,10 +2388,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130256321</v>
+        <v>130256006</v>
       </c>
       <c r="B18" t="n">
-        <v>78969</v>
+        <v>79211</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2399,21 +2399,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2423,10 +2423,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496183</v>
+        <v>496064</v>
       </c>
       <c r="R18" t="n">
-        <v>6828767</v>
+        <v>6829002</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2456,9 +2456,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2473,22 +2483,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130256006</v>
+        <v>130256321</v>
       </c>
       <c r="B19" t="n">
-        <v>79211</v>
+        <v>78969</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2496,21 +2506,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2520,10 +2530,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496064</v>
+        <v>496183</v>
       </c>
       <c r="R19" t="n">
-        <v>6829002</v>
+        <v>6828767</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2553,19 +2563,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2580,12 +2580,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2806,45 +2806,56 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130256003</v>
+        <v>130256007</v>
       </c>
       <c r="B22" t="n">
-        <v>79211</v>
+        <v>93047</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hammarberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496231</v>
+        <v>496230</v>
       </c>
       <c r="R22" t="n">
-        <v>6829125</v>
+        <v>6828797</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2876,7 +2887,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2886,7 +2897,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2895,6 +2906,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2913,56 +2925,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130256007</v>
+        <v>130256003</v>
       </c>
       <c r="B23" t="n">
-        <v>93047</v>
+        <v>79211</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hammarberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496230</v>
+        <v>496231</v>
       </c>
       <c r="R23" t="n">
-        <v>6828797</v>
+        <v>6829125</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2994,7 +2995,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3004,7 +3005,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3013,7 +3014,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3246,10 +3246,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130256004</v>
+        <v>130256320</v>
       </c>
       <c r="B26" t="n">
-        <v>79211</v>
+        <v>78969</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3257,21 +3257,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496212</v>
+        <v>496252</v>
       </c>
       <c r="R26" t="n">
-        <v>6829243</v>
+        <v>6828819</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3314,19 +3314,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3341,22 +3331,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130256320</v>
+        <v>130256004</v>
       </c>
       <c r="B27" t="n">
-        <v>78969</v>
+        <v>79211</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3364,21 +3354,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3388,10 +3378,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496252</v>
+        <v>496212</v>
       </c>
       <c r="R27" t="n">
-        <v>6828819</v>
+        <v>6829243</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3421,9 +3411,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3438,12 +3438,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 55957-2025 artfynd.xlsx
+++ b/artfynd/A 55957-2025 artfynd.xlsx
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130252658</v>
+        <v>130252213</v>
       </c>
       <c r="B3" t="n">
-        <v>78968</v>
+        <v>93047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496322</v>
+        <v>496229</v>
       </c>
       <c r="R3" t="n">
-        <v>6828932</v>
+        <v>6828807</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,44 +877,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130252213</v>
+        <v>130252658</v>
       </c>
       <c r="B4" t="n">
-        <v>93047</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496229</v>
+        <v>496322</v>
       </c>
       <c r="R4" t="n">
-        <v>6828807</v>
+        <v>6828932</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,12 +984,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130256320</v>
+        <v>130256004</v>
       </c>
       <c r="B26" t="n">
-        <v>78969</v>
+        <v>79211</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3257,21 +3257,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496252</v>
+        <v>496212</v>
       </c>
       <c r="R26" t="n">
-        <v>6828819</v>
+        <v>6829243</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3314,9 +3314,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3331,22 +3341,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130256004</v>
+        <v>130256320</v>
       </c>
       <c r="B27" t="n">
-        <v>79211</v>
+        <v>78969</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3354,21 +3364,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3378,10 +3388,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496212</v>
+        <v>496252</v>
       </c>
       <c r="R27" t="n">
-        <v>6829243</v>
+        <v>6828819</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3411,19 +3421,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3438,12 +3438,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 55957-2025 artfynd.xlsx
+++ b/artfynd/A 55957-2025 artfynd.xlsx
@@ -2388,10 +2388,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130256006</v>
+        <v>130256321</v>
       </c>
       <c r="B18" t="n">
-        <v>79211</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2399,21 +2399,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2423,10 +2423,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496064</v>
+        <v>496183</v>
       </c>
       <c r="R18" t="n">
-        <v>6829002</v>
+        <v>6828767</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2456,19 +2456,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2483,22 +2473,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130256321</v>
+        <v>130256006</v>
       </c>
       <c r="B19" t="n">
-        <v>78969</v>
+        <v>79219</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2506,21 +2496,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2530,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496183</v>
+        <v>496064</v>
       </c>
       <c r="R19" t="n">
-        <v>6828767</v>
+        <v>6829002</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2563,9 +2553,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2580,12 +2580,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2595,7 +2595,7 @@
         <v>130256005</v>
       </c>
       <c r="B20" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>130256002</v>
       </c>
       <c r="B21" t="n">
-        <v>78968</v>
+        <v>78976</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2806,56 +2806,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130256007</v>
+        <v>130256003</v>
       </c>
       <c r="B22" t="n">
-        <v>93047</v>
+        <v>79219</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hammarberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496230</v>
+        <v>496231</v>
       </c>
       <c r="R22" t="n">
-        <v>6828797</v>
+        <v>6829125</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2887,7 +2876,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2897,7 +2886,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2906,7 +2895,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2925,45 +2913,56 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130256003</v>
+        <v>130256007</v>
       </c>
       <c r="B23" t="n">
-        <v>79211</v>
+        <v>93060</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hammarberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496231</v>
+        <v>496230</v>
       </c>
       <c r="R23" t="n">
-        <v>6829125</v>
+        <v>6828797</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2995,7 +2994,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3005,7 +3004,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,6 +3013,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3035,7 +3035,7 @@
         <v>130256000</v>
       </c>
       <c r="B24" t="n">
-        <v>91745</v>
+        <v>91758</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>130256001</v>
       </c>
       <c r="B25" t="n">
-        <v>78968</v>
+        <v>78976</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3246,10 +3246,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130256004</v>
+        <v>130256320</v>
       </c>
       <c r="B26" t="n">
-        <v>79211</v>
+        <v>78977</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3257,21 +3257,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496212</v>
+        <v>496252</v>
       </c>
       <c r="R26" t="n">
-        <v>6829243</v>
+        <v>6828819</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3314,19 +3314,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3341,22 +3331,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130256320</v>
+        <v>130256004</v>
       </c>
       <c r="B27" t="n">
-        <v>78969</v>
+        <v>79219</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3364,21 +3354,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3388,10 +3378,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496252</v>
+        <v>496212</v>
       </c>
       <c r="R27" t="n">
-        <v>6828819</v>
+        <v>6829243</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3421,9 +3411,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3438,12 +3438,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 55957-2025 artfynd.xlsx
+++ b/artfynd/A 55957-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130252661</v>
+        <v>130252213</v>
       </c>
       <c r="B2" t="n">
-        <v>78968</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496186</v>
+        <v>496229</v>
       </c>
       <c r="R2" t="n">
-        <v>6828768</v>
+        <v>6828807</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,26 +770,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130252213</v>
+        <v>130252662</v>
       </c>
       <c r="B3" t="n">
-        <v>93047</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496229</v>
+        <v>496302</v>
       </c>
       <c r="R3" t="n">
-        <v>6828807</v>
+        <v>6828945</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,28 +871,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130252658</v>
+        <v>130256007</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +901,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hammarberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496322</v>
+        <v>496230</v>
       </c>
       <c r="R4" t="n">
-        <v>6828932</v>
+        <v>6828797</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -978,50 +990,51 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130252204</v>
+        <v>130256000</v>
       </c>
       <c r="B5" t="n">
-        <v>79830</v>
+        <v>91893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>4660</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496196</v>
+        <v>496087</v>
       </c>
       <c r="R5" t="n">
-        <v>6829176</v>
+        <v>6828938</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1079,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1089,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,44 +1104,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130252214</v>
+        <v>130256006</v>
       </c>
       <c r="B6" t="n">
-        <v>93047</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496220</v>
+        <v>496064</v>
       </c>
       <c r="R6" t="n">
-        <v>6829188</v>
+        <v>6829002</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1186,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1196,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,44 +1211,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130252205</v>
+        <v>130252658</v>
       </c>
       <c r="B7" t="n">
-        <v>8451</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496203</v>
+        <v>496322</v>
       </c>
       <c r="R7" t="n">
-        <v>6829246</v>
+        <v>6828932</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1293,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1303,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,44 +1318,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130252208</v>
+        <v>130252659</v>
       </c>
       <c r="B8" t="n">
-        <v>8451</v>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496072</v>
+        <v>496262</v>
       </c>
       <c r="R8" t="n">
-        <v>6828986</v>
+        <v>6828867</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1400,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1410,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1412,44 +1425,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130252207</v>
+        <v>130252660</v>
       </c>
       <c r="B9" t="n">
-        <v>8451</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496116</v>
+        <v>496248</v>
       </c>
       <c r="R9" t="n">
-        <v>6829108</v>
+        <v>6828803</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1507,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1517,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1519,44 +1532,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130252662</v>
+        <v>130252661</v>
       </c>
       <c r="B10" t="n">
-        <v>93047</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1579,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496302</v>
+        <v>496186</v>
       </c>
       <c r="R10" t="n">
-        <v>6828945</v>
+        <v>6828768</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1614,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1624,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1620,7 +1633,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1639,10 +1651,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130252211</v>
+        <v>130256002</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,10 +1686,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496196</v>
+        <v>496059</v>
       </c>
       <c r="R11" t="n">
-        <v>6829176</v>
+        <v>6829006</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1721,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1719,7 +1731,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,22 +1746,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130252206</v>
+        <v>130252208</v>
       </c>
       <c r="B12" t="n">
-        <v>8451</v>
+        <v>8455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,10 +1793,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496198</v>
+        <v>496072</v>
       </c>
       <c r="R12" t="n">
-        <v>6829176</v>
+        <v>6828986</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,7 +1828,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1826,7 +1838,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1853,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130252212</v>
+        <v>130256320</v>
       </c>
       <c r="B13" t="n">
-        <v>79211</v>
+        <v>79085</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1864,21 +1876,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1888,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496212</v>
+        <v>496252</v>
       </c>
       <c r="R13" t="n">
-        <v>6829184</v>
+        <v>6828819</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1921,19 +1933,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:35</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1948,22 +1950,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130252209</v>
+        <v>130256321</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>79085</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,21 +1973,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1995,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496215</v>
+        <v>496183</v>
       </c>
       <c r="R14" t="n">
-        <v>6829262</v>
+        <v>6828767</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2028,19 +2030,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2055,22 +2047,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130252660</v>
+        <v>130252214</v>
       </c>
       <c r="B15" t="n">
-        <v>78968</v>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2078,21 +2070,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2102,10 +2094,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496248</v>
+        <v>496220</v>
       </c>
       <c r="R15" t="n">
-        <v>6828803</v>
+        <v>6829188</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,7 +2129,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2147,7 +2139,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2162,44 +2154,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130252210</v>
+        <v>130252212</v>
       </c>
       <c r="B16" t="n">
-        <v>78968</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2201,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496222</v>
+        <v>496212</v>
       </c>
       <c r="R16" t="n">
-        <v>6829194</v>
+        <v>6829184</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2244,7 +2236,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2254,7 +2246,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2281,32 +2273,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130252659</v>
+        <v>130256003</v>
       </c>
       <c r="B17" t="n">
-        <v>78968</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2316,10 +2308,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496262</v>
+        <v>496231</v>
       </c>
       <c r="R17" t="n">
-        <v>6828867</v>
+        <v>6829125</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2351,7 +2343,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2361,7 +2353,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2376,44 +2368,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130256321</v>
+        <v>130256004</v>
       </c>
       <c r="B18" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2423,10 +2415,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496183</v>
+        <v>496212</v>
       </c>
       <c r="R18" t="n">
-        <v>6828767</v>
+        <v>6829243</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2456,9 +2448,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2473,26 +2475,26 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130256006</v>
+        <v>130256005</v>
       </c>
       <c r="B19" t="n">
-        <v>79219</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2520,10 +2522,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496064</v>
+        <v>496177</v>
       </c>
       <c r="R19" t="n">
-        <v>6829002</v>
+        <v>6829128</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2555,7 +2557,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2565,7 +2567,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2592,10 +2594,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130256005</v>
+        <v>130252209</v>
       </c>
       <c r="B20" t="n">
-        <v>79219</v>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2603,21 +2605,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2627,10 +2629,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496177</v>
+        <v>496215</v>
       </c>
       <c r="R20" t="n">
-        <v>6829128</v>
+        <v>6829262</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2662,7 +2664,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2672,7 +2674,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2687,22 +2689,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130256002</v>
+        <v>130252210</v>
       </c>
       <c r="B21" t="n">
-        <v>78976</v>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,10 +2736,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496059</v>
+        <v>496222</v>
       </c>
       <c r="R21" t="n">
-        <v>6829006</v>
+        <v>6829194</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2769,7 +2771,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2779,7 +2781,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2794,22 +2796,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130256003</v>
+        <v>130252211</v>
       </c>
       <c r="B22" t="n">
-        <v>79219</v>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2817,21 +2819,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2841,10 +2843,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496231</v>
+        <v>496196</v>
       </c>
       <c r="R22" t="n">
-        <v>6829125</v>
+        <v>6829176</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2876,7 +2878,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2886,7 +2888,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2901,68 +2903,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130256007</v>
+        <v>130256001</v>
       </c>
       <c r="B23" t="n">
-        <v>93060</v>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hammarberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496230</v>
+        <v>496196</v>
       </c>
       <c r="R23" t="n">
-        <v>6828797</v>
+        <v>6829166</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2994,7 +2985,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3004,7 +2995,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3013,7 +3004,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3032,32 +3022,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130256000</v>
+        <v>130252204</v>
       </c>
       <c r="B24" t="n">
-        <v>91758</v>
+        <v>79946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4660</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3067,10 +3057,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496087</v>
+        <v>496196</v>
       </c>
       <c r="R24" t="n">
-        <v>6828938</v>
+        <v>6829176</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3102,7 +3092,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3112,7 +3102,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3127,44 +3117,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130256001</v>
+        <v>130252205</v>
       </c>
       <c r="B25" t="n">
-        <v>78976</v>
+        <v>8455</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3174,10 +3164,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496196</v>
+        <v>496203</v>
       </c>
       <c r="R25" t="n">
-        <v>6829166</v>
+        <v>6829246</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3209,7 +3199,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3219,7 +3209,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3234,44 +3224,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130256320</v>
+        <v>130252206</v>
       </c>
       <c r="B26" t="n">
-        <v>78977</v>
+        <v>8455</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3281,10 +3271,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496252</v>
+        <v>496198</v>
       </c>
       <c r="R26" t="n">
-        <v>6828819</v>
+        <v>6829176</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3314,9 +3304,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3331,44 +3331,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130256004</v>
+        <v>130252207</v>
       </c>
       <c r="B27" t="n">
-        <v>79219</v>
+        <v>8455</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496212</v>
+        <v>496116</v>
       </c>
       <c r="R27" t="n">
-        <v>6829243</v>
+        <v>6829108</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3438,12 +3438,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 55957-2025 artfynd.xlsx
+++ b/artfynd/A 55957-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252213</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252214</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252662</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256007</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1220,6 +1245,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256000</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1327,6 +1357,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252212</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1434,6 +1469,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256003</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1541,6 +1581,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256004</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1648,6 +1693,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256005</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1755,6 +1805,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256006</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1862,6 +1917,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252209</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1969,6 +2029,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252210</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2076,6 +2141,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252211</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2183,6 +2253,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252658</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2290,6 +2365,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252659</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2397,6 +2477,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252660</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2504,6 +2589,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252661</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2611,6 +2701,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256001</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2718,6 +2813,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256002</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2825,6 +2925,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252204</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2932,6 +3037,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252205</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3039,6 +3149,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252206</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3146,6 +3261,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252207</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3253,6 +3373,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252208</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3350,6 +3475,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256320</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3447,8 +3577,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256321</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>